--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -1641,8 +1641,10 @@
       <x:c r="A10" s="106" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="109" t="str">
-        <x:v>Apply meaningful date, whole-number, and business currency formats.</x:v>
+      <x:c r="B10" s="109" t="inlineStr">
+        <x:is>
+          <x:t>Apply meaningful date and business currency formats; format counts as Number with 0 decimal places.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C10"/>
       <x:c r="D10"/>
@@ -1764,8 +1766,10 @@
       <x:c r="E4" s="104"/>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="127" t="str">
-        <x:v>WHAT + HOW · Format Sale Date as a readable date, Units Sold as a whole number, and Sales Revenue / Gross Profit as business money. Then make the headers and widths easy to scan.</x:v>
+      <x:c r="A5" s="127" t="inlineStr">
+        <x:is>
+          <x:t>Format Sale Date as a readable date and Sales Revenue / Gross Profit as money. For Units Sold, select C8:C13 → Home → Number → Number; use Decrease Decimal to show 0 decimal places (38, not 38.00). Then adjust headings and widths.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B5" s="128"/>
       <x:c r="C5" s="128"/>
@@ -1979,8 +1983,10 @@
       <x:c r="A24" s="172" t="str">
         <x:v>□</x:v>
       </x:c>
-      <x:c r="B24" s="175" t="str">
-        <x:v>Dates, whole-number counts, and money are immediately recognizable.</x:v>
+      <x:c r="B24" s="175" t="inlineStr">
+        <x:is>
+          <x:t>Dates, counts formatted as Number with 0 decimal places, and money are immediately recognizable.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C24" s="175"/>
       <x:c r="D24" s="175"/>
@@ -3399,8 +3405,10 @@
       <x:c r="A8" s="262" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="259" t="str">
-        <x:v>Use meaningful formats for the date, whole-number Guests, and business-money columns.</x:v>
+      <x:c r="B8" s="259" t="inlineStr">
+        <x:is>
+          <x:t>Use meaningful formats for the date and business-money columns; format Guests as Number with 0 decimal places.</x:t>
+        </x:is>
       </x:c>
       <x:c r="C8" s="259" t="str">
         <x:v>Manager View</x:v>

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R68b84be923024d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rb1c8ca2660f14d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Ref2fb5b8544240bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R9a90e5102b4f45db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R8eff6ffd248f44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="Re671bd319c664391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R72a994129d7747d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rf2b400f1a18d4ceb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R6d5b163d92d64bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R6e5a3681691f4191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R832a3967bb7f4c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R705248219de64397"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
     <x:numFmt numFmtId="201" formatCode="General"/>
+    <x:numFmt numFmtId="202" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -162,8 +163,25 @@
       <x:color rgb="FF355773"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF18261D"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF18261D"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="26">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -275,6 +293,21 @@
         <x:fgColor rgb="FFEAF3EC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF217346"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2C7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="48">
     <x:border/>
@@ -736,7 +769,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="290">
+  <x:cellXfs count="302">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1366,6 +1399,40 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="22" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1643,7 +1710,7 @@
       </x:c>
       <x:c r="B10" s="109" t="inlineStr">
         <x:is>
-          <x:t>Apply meaningful date and business currency formats; format counts as Number with 0 decimal places.</x:t>
+          <x:t xml:space="preserve">Apply meaningful date and business currency formats; format counts as Number with 0 decimal places.</x:t>
         </x:is>
       </x:c>
       <x:c r="C10"/>
@@ -1731,339 +1798,564 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="114" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="294" t="str">
         <x:v>Tidal Goods Co. · Live You Try It</x:v>
       </x:c>
-      <x:c r="B1" s="114"/>
-      <x:c r="C1" s="114"/>
-      <x:c r="D1" s="114"/>
-      <x:c r="E1" s="114"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="117" t="str">
-        <x:v>This guided retail dataset is different from the graded Anchor &amp; Oak challenge. Make formatting decisions without changing the supplied values. This sheet is not graded.</x:v>
-      </x:c>
-      <x:c r="B2" s="117"/>
-      <x:c r="C2" s="117"/>
-      <x:c r="D2" s="117"/>
-      <x:c r="E2" s="117"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="104" t="str">
-        <x:v>Checkpoint 1 · 6 minutes · Make the supplied retail records readable</x:v>
-      </x:c>
-      <x:c r="B4" s="104"/>
-      <x:c r="C4" s="104"/>
-      <x:c r="D4" s="104"/>
-      <x:c r="E4" s="104"/>
-    </x:row>
-    <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="127" t="inlineStr">
-        <x:is>
-          <x:t>Format Sale Date as a readable date and Sales Revenue / Gross Profit as money. For Units Sold, select C8:C13 → Home → Number → Number; use Decrease Decimal to show 0 decimal places (38, not 38.00). Then adjust headings and widths.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="128"/>
-      <x:c r="C5" s="128"/>
-      <x:c r="D5" s="128"/>
-      <x:c r="E5" s="129"/>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="130" t="str">
-        <x:v>DELIVERABLE · A six-row practice table whose dates, counts, money, labels, and alignment communicate clearly without changing any supplied value.</x:v>
-      </x:c>
-      <x:c r="B6" s="131"/>
-      <x:c r="C6" s="131"/>
-      <x:c r="D6" s="131"/>
-      <x:c r="E6" s="132"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="136" t="str">
+      <x:c r="B1" s="294"/>
+      <x:c r="C1" s="294"/>
+      <x:c r="D1" s="294"/>
+      <x:c r="E1" s="294"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
+      <x:c r="A2" s="291"/>
+      <x:c r="B2" s="291"/>
+      <x:c r="C2" s="291"/>
+      <x:c r="D2" s="291"/>
+      <x:c r="E2" s="291"/>
+    </x:row>
+    <x:row r="3" ht="8" customHeight="1">
+      <x:c r="A3" s="291"/>
+      <x:c r="B3" s="291"/>
+      <x:c r="C3" s="291"/>
+      <x:c r="D3" s="291"/>
+      <x:c r="E3" s="291"/>
+    </x:row>
+    <x:row r="4" ht="8" customHeight="1">
+      <x:c r="A4" s="291"/>
+      <x:c r="B4" s="291"/>
+      <x:c r="C4" s="291"/>
+      <x:c r="D4" s="291"/>
+      <x:c r="E4" s="291"/>
+    </x:row>
+    <x:row r="5" ht="8" customHeight="1">
+      <x:c r="A5" s="291"/>
+      <x:c r="B5" s="291"/>
+      <x:c r="C5" s="291"/>
+      <x:c r="D5" s="291"/>
+      <x:c r="E5" s="291"/>
+    </x:row>
+    <x:row r="6" ht="8" customHeight="1">
+      <x:c r="A6" s="291"/>
+      <x:c r="B6" s="291"/>
+      <x:c r="C6" s="291"/>
+      <x:c r="D6" s="291"/>
+      <x:c r="E6" s="291"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="296" t="str">
         <x:v>Product</x:v>
       </x:c>
-      <x:c r="B7" s="136" t="str">
+      <x:c r="B7" s="296" t="str">
         <x:v>Sale Date</x:v>
       </x:c>
-      <x:c r="C7" s="136" t="str">
+      <x:c r="C7" s="296" t="str">
         <x:v>Units Sold</x:v>
       </x:c>
-      <x:c r="D7" s="136" t="str">
+      <x:c r="D7" s="296" t="str">
         <x:v>Sales Revenue</x:v>
       </x:c>
-      <x:c r="E7" s="136" t="str">
+      <x:c r="E7" s="296" t="str">
         <x:v>Gross Profit</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="139" t="str">
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="297" t="str">
         <x:v>Coastal Tote</x:v>
       </x:c>
-      <x:c r="B8" s="140" t="n">
+      <x:c r="B8" s="297" t="n">
         <x:v>46087</x:v>
       </x:c>
-      <x:c r="C8" s="140" t="n">
+      <x:c r="C8" s="297" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D8" s="140" t="n">
+      <x:c r="D8" s="297" t="n">
         <x:v>3040</x:v>
       </x:c>
-      <x:c r="E8" s="140" t="n">
+      <x:c r="E8" s="297" t="n">
         <x:v>1216</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="139" t="str">
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="297" t="str">
         <x:v>Insulated Bottle</x:v>
       </x:c>
-      <x:c r="B9" s="140" t="n">
+      <x:c r="B9" s="297" t="n">
         <x:v>46095</x:v>
       </x:c>
-      <x:c r="C9" s="140" t="n">
+      <x:c r="C9" s="297" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D9" s="140" t="n">
+      <x:c r="D9" s="297" t="n">
         <x:v>1680</x:v>
       </x:c>
-      <x:c r="E9" s="140" t="n">
+      <x:c r="E9" s="297" t="n">
         <x:v>672</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="139" t="str">
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="297" t="str">
         <x:v>Canvas Apron</x:v>
       </x:c>
-      <x:c r="B10" s="140" t="n">
+      <x:c r="B10" s="297" t="n">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="C10" s="140" t="n">
+      <x:c r="C10" s="297" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D10" s="140" t="n">
+      <x:c r="D10" s="297" t="n">
         <x:v>1360</x:v>
       </x:c>
-      <x:c r="E10" s="140" t="n">
+      <x:c r="E10" s="297" t="n">
         <x:v>544</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="139" t="str">
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="297" t="str">
         <x:v>Bamboo Tray</x:v>
       </x:c>
-      <x:c r="B11" s="140" t="n">
+      <x:c r="B11" s="297" t="n">
         <x:v>46131</x:v>
       </x:c>
-      <x:c r="C11" s="140" t="n">
+      <x:c r="C11" s="297" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="140" t="n">
+      <x:c r="D11" s="297" t="n">
         <x:v>2480</x:v>
       </x:c>
-      <x:c r="E11" s="140" t="n">
+      <x:c r="E11" s="297" t="n">
         <x:v>868</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="139" t="str">
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="297" t="str">
         <x:v>Ceramic Mug</x:v>
       </x:c>
-      <x:c r="B12" s="140" t="n">
+      <x:c r="B12" s="297" t="n">
         <x:v>46149</x:v>
       </x:c>
-      <x:c r="C12" s="140" t="n">
+      <x:c r="C12" s="297" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D12" s="140" t="n">
+      <x:c r="D12" s="297" t="n">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="E12" s="140" t="n">
+      <x:c r="E12" s="297" t="n">
         <x:v>810</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="139" t="str">
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="297" t="str">
         <x:v>Storage Basket</x:v>
       </x:c>
-      <x:c r="B13" s="140" t="n">
+      <x:c r="B13" s="297" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="C13" s="140" t="n">
+      <x:c r="C13" s="297" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D13" s="140" t="n">
+      <x:c r="D13" s="297" t="n">
         <x:v>1520</x:v>
       </x:c>
-      <x:c r="E13" s="140" t="n">
+      <x:c r="E13" s="297" t="n">
         <x:v>532</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="142" t="str">
-        <x:v>Checkpoint 2 · 5 minutes · Make the table usable</x:v>
-      </x:c>
-      <x:c r="B15" s="142"/>
-      <x:c r="C15" s="142"/>
-      <x:c r="D15" s="142"/>
-      <x:c r="E15" s="142"/>
-    </x:row>
-    <x:row r="16" ht="58" customHeight="1">
-      <x:c r="A16" s="146" t="str">
-        <x:v>WHAT + HOW · Convert A7:E13 to an Excel table, keep its filters, select A8 and freeze the rows above it, then apply one conditional-formatting rule to E8:E13 for a retail decision you can explain.</x:v>
-      </x:c>
-      <x:c r="B16" s="147"/>
-      <x:c r="C16" s="147"/>
-      <x:c r="D16" s="147"/>
-      <x:c r="E16" s="148"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="150" t="str">
-        <x:v>DELIVERABLE · A working table plus one purpose statement</x:v>
-      </x:c>
-      <x:c r="B18" s="150"/>
-      <x:c r="C18" s="150"/>
-      <x:c r="D18" s="150"/>
-      <x:c r="E18" s="150"/>
-    </x:row>
-    <x:row r="19" ht="34" customHeight="1">
-      <x:c r="A19" s="165" t="str">
-        <x:v>Type here: Highlight __________ because the retail manager needs to __________.</x:v>
-      </x:c>
-      <x:c r="B19" s="166"/>
-      <x:c r="C19" s="166"/>
-      <x:c r="D19" s="166"/>
-      <x:c r="E19" s="167"/>
-    </x:row>
-    <x:row r="20" ht="34" customHeight="1">
-      <x:c r="A20" s="168"/>
-      <x:c r="B20" s="169"/>
-      <x:c r="C20" s="169"/>
-      <x:c r="D20" s="169"/>
-      <x:c r="E20" s="170"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="104" t="str">
-        <x:v>Quick self-check before the Anchor &amp; Oak challenge</x:v>
-      </x:c>
-      <x:c r="B22" s="104"/>
-      <x:c r="C22" s="104"/>
-      <x:c r="D22" s="104"/>
-      <x:c r="E22" s="104"/>
-    </x:row>
-    <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="172" t="str">
-        <x:v>□</x:v>
-      </x:c>
-      <x:c r="B23" s="175" t="str">
-        <x:v>The same stored values remain in every Tidal Goods practice cell.</x:v>
-      </x:c>
-      <x:c r="C23" s="175"/>
-      <x:c r="D23" s="175"/>
-      <x:c r="E23" s="175"/>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="172" t="str">
-        <x:v>□</x:v>
-      </x:c>
-      <x:c r="B24" s="175" t="inlineStr">
-        <x:is>
-          <x:t>Dates, counts formatted as Number with 0 decimal places, and money are immediately recognizable.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="175"/>
-      <x:c r="D24" s="175"/>
-      <x:c r="E24" s="175"/>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="172" t="str">
-        <x:v>□</x:v>
-      </x:c>
-      <x:c r="B25" s="175" t="str">
-        <x:v>The row 7 header remains visible when you scroll below the table.</x:v>
-      </x:c>
-      <x:c r="C25" s="175"/>
-      <x:c r="D25" s="175"/>
-      <x:c r="E25" s="175"/>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="172" t="str">
-        <x:v>□</x:v>
-      </x:c>
-      <x:c r="B26" s="175" t="str">
-        <x:v>You can explain what your conditional-formatting rule helps a retail manager notice.</x:v>
-      </x:c>
-      <x:c r="C26" s="175"/>
-      <x:c r="D26" s="175"/>
-      <x:c r="E26" s="175"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="297" t="str">
+        <x:v>Linen Napkins</x:v>
+      </x:c>
+      <x:c r="B14" s="297" t="n">
+        <x:v>46166</x:v>
+      </x:c>
+      <x:c r="C14" s="297" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="297" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="E14" s="297" t="n">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="297" t="str">
+        <x:v>Glass Pitcher</x:v>
+      </x:c>
+      <x:c r="B15" s="297" t="n">
+        <x:v>46167</x:v>
+      </x:c>
+      <x:c r="C15" s="297" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D15" s="297" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="E15" s="297" t="n">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="297" t="str">
+        <x:v>Wooden Coasters</x:v>
+      </x:c>
+      <x:c r="B16" s="297" t="n">
+        <x:v>46168</x:v>
+      </x:c>
+      <x:c r="C16" s="297" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="297" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="E16" s="297" t="n">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="297" t="str">
+        <x:v>Beach Blanket</x:v>
+      </x:c>
+      <x:c r="B17" s="297" t="n">
+        <x:v>46169</x:v>
+      </x:c>
+      <x:c r="C17" s="297" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D17" s="297" t="n">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="E17" s="297" t="n">
+        <x:v>567</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="297" t="str">
+        <x:v>Travel Pouch</x:v>
+      </x:c>
+      <x:c r="B18" s="297" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C18" s="297" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D18" s="297" t="n">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="E18" s="297" t="n">
+        <x:v>262.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="297" t="str">
+        <x:v>Serving Board</x:v>
+      </x:c>
+      <x:c r="B19" s="297" t="n">
+        <x:v>46171</x:v>
+      </x:c>
+      <x:c r="C19" s="297" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D19" s="297" t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="E19" s="297" t="n">
+        <x:v>346.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="297" t="str">
+        <x:v>Desk Organizer</x:v>
+      </x:c>
+      <x:c r="B20" s="297" t="n">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="C20" s="297" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D20" s="297" t="n">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="E20" s="297" t="n">
+        <x:v>350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="297" t="str">
+        <x:v>Lunch Bag</x:v>
+      </x:c>
+      <x:c r="B21" s="297" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+      <x:c r="C21" s="297" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D21" s="297" t="n">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="E21" s="297" t="n">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="297" t="str">
+        <x:v>Tea Towel</x:v>
+      </x:c>
+      <x:c r="B22" s="297" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="C22" s="297" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D22" s="297" t="n">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="E22" s="297" t="n">
+        <x:v>172.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="297" t="str">
+        <x:v>Candle Holder</x:v>
+      </x:c>
+      <x:c r="B23" s="297" t="n">
+        <x:v>46175</x:v>
+      </x:c>
+      <x:c r="C23" s="297" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D23" s="297" t="n">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="E23" s="297" t="n">
+        <x:v>225.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="297" t="str">
+        <x:v>Water Carafe</x:v>
+      </x:c>
+      <x:c r="B24" s="297" t="n">
+        <x:v>46176</x:v>
+      </x:c>
+      <x:c r="C24" s="297" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D24" s="297" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="E24" s="297" t="n">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="297" t="str">
+        <x:v>Cotton Throw</x:v>
+      </x:c>
+      <x:c r="B25" s="297" t="n">
+        <x:v>46177</x:v>
+      </x:c>
+      <x:c r="C25" s="297" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D25" s="297" t="n">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="E25" s="297" t="n">
+        <x:v>585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="297" t="str">
+        <x:v>Plant Pot</x:v>
+      </x:c>
+      <x:c r="B26" s="297" t="n">
+        <x:v>46178</x:v>
+      </x:c>
+      <x:c r="C26" s="297" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D26" s="297" t="n">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="E26" s="297" t="n">
+        <x:v>244.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="297" t="str">
+        <x:v>Picnic Basket</x:v>
+      </x:c>
+      <x:c r="B27" s="297" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="C27" s="297" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D27" s="297" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="E27" s="297" t="n">
+        <x:v>378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="297" t="str">
+        <x:v>Soap Dish</x:v>
+      </x:c>
+      <x:c r="B28" s="297" t="n">
+        <x:v>46180</x:v>
+      </x:c>
+      <x:c r="C28" s="297" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D28" s="297" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="E28" s="297" t="n">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="297" t="str">
+        <x:v>Table Runner</x:v>
+      </x:c>
+      <x:c r="B29" s="297" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="C29" s="297" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D29" s="297" t="n">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="E29" s="297" t="n">
+        <x:v>388.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="297" t="str">
+        <x:v>Storage Jar</x:v>
+      </x:c>
+      <x:c r="B30" s="297" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="C30" s="297" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D30" s="297" t="n">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="E30" s="297" t="n">
+        <x:v>178.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="297" t="str">
+        <x:v>Oven Mitt</x:v>
+      </x:c>
+      <x:c r="B31" s="297" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="C31" s="297" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D31" s="297" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="E31" s="297" t="n">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="297" t="str">
+        <x:v>Woven Placemat</x:v>
+      </x:c>
+      <x:c r="B32" s="297" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="C32" s="297" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D32" s="297" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E32" s="297" t="n">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="297" t="str">
+        <x:v>Reusable Wraps</x:v>
+      </x:c>
+      <x:c r="B33" s="297" t="n">
+        <x:v>46185</x:v>
+      </x:c>
+      <x:c r="C33" s="297" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D33" s="297" t="n">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="E33" s="297" t="n">
+        <x:v>257.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="291"/>
+      <x:c r="B34" s="291"/>
+      <x:c r="C34" s="291"/>
+      <x:c r="D34" s="291"/>
+      <x:c r="E34" s="291"/>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="298" t="str">
+        <x:v>Explain your alert: what should the retail manager notice, and why?</x:v>
+      </x:c>
+      <x:c r="B35" s="298"/>
+      <x:c r="C35" s="298"/>
+      <x:c r="D35" s="298"/>
+      <x:c r="E35" s="298"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="299" t="str"/>
+      <x:c r="B36" s="299"/>
+      <x:c r="C36" s="299"/>
+      <x:c r="D36" s="299"/>
+      <x:c r="E36" s="299"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="291" t="str">
+        <x:v>Total Sales Revenue</x:v>
+      </x:c>
+      <x:c r="B37" s="291"/>
+      <x:c r="C37" s="291"/>
+      <x:c r="D37" s="291"/>
+      <x:c r="E37" s="301"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="291" t="str">
+        <x:v>Average Sales Revenue / Product</x:v>
+      </x:c>
+      <x:c r="B38" s="291"/>
+      <x:c r="C38" s="291"/>
+      <x:c r="D38" s="291"/>
+      <x:c r="E38" s="301"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:E2"/>
-    <x:mergeCell ref="A4:E4"/>
-    <x:mergeCell ref="A5:E5"/>
-    <x:mergeCell ref="A6:E6"/>
-    <x:mergeCell ref="A15:E15"/>
-    <x:mergeCell ref="A16:E16"/>
-    <x:mergeCell ref="A18:E18"/>
-    <x:mergeCell ref="A19:E20"/>
-    <x:mergeCell ref="A22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="A35:E35"/>
+    <x:mergeCell ref="A36:E36"/>
+    <x:mergeCell ref="A37:D37"/>
+    <x:mergeCell ref="A38:D38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3407,7 +3699,7 @@
       </x:c>
       <x:c r="B8" s="259" t="inlineStr">
         <x:is>
-          <x:t>Use meaningful formats for the date and business-money columns; format Guests as Number with 0 decimal places.</x:t>
+          <x:t xml:space="preserve">Use meaningful formats for the date and business-money columns; format Guests as Number with 0 decimal places.</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" s="259" t="str">

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R72a994129d7747d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rf2b400f1a18d4ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R6d5b163d92d64bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R6e5a3681691f4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R832a3967bb7f4c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R705248219de64397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rf3f1bc7609974853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R76648c344d7c462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Rc86fca8b89dc4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R2fbc0c0332ac4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="Rc700cf8344d24302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R7fe12204bc094ad1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,10 +18,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="$#,##0"/>
     <x:numFmt numFmtId="201" formatCode="General"/>
-    <x:numFmt numFmtId="202" formatCode="$#,##0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0.0"/>
+    <x:numFmt numFmtId="203" formatCode="0.000"/>
+    <x:numFmt numFmtId="204" formatCode="0.00"/>
+    <x:numFmt numFmtId="205" formatCode="0"/>
+    <x:numFmt numFmtId="206" formatCode="0.0000"/>
+    <x:numFmt numFmtId="207" formatCode="$#,##0.00"/>
   </x:numFmts>
   <x:fonts count="27">
     <x:font>
@@ -181,7 +186,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="26">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -300,11 +305,6 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF3EC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2C7"/>
       </x:patternFill>
     </x:fill>
@@ -769,7 +769,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="302">
+  <x:cellXfs count="306">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1422,16 +1422,28 @@
     <x:xf numFmtId="201" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="24" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="207" fontId="24" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1801,8 +1813,9 @@
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1813,6 +1826,7 @@
       <x:c r="C1" s="294"/>
       <x:c r="D1" s="294"/>
       <x:c r="E1" s="294"/>
+      <x:c r="F1" s="294"/>
     </x:row>
     <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="291"/>
@@ -1820,6 +1834,7 @@
       <x:c r="C2" s="291"/>
       <x:c r="D2" s="291"/>
       <x:c r="E2" s="291"/>
+      <x:c r="F2" s="291"/>
     </x:row>
     <x:row r="3" ht="8" customHeight="1">
       <x:c r="A3" s="291"/>
@@ -1827,6 +1842,7 @@
       <x:c r="C3" s="291"/>
       <x:c r="D3" s="291"/>
       <x:c r="E3" s="291"/>
+      <x:c r="F3" s="291"/>
     </x:row>
     <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="291"/>
@@ -1834,6 +1850,7 @@
       <x:c r="C4" s="291"/>
       <x:c r="D4" s="291"/>
       <x:c r="E4" s="291"/>
+      <x:c r="F4" s="291"/>
     </x:row>
     <x:row r="5" ht="8" customHeight="1">
       <x:c r="A5" s="291"/>
@@ -1841,6 +1858,7 @@
       <x:c r="C5" s="291"/>
       <x:c r="D5" s="291"/>
       <x:c r="E5" s="291"/>
+      <x:c r="F5" s="291"/>
     </x:row>
     <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="291"/>
@@ -1848,6 +1866,7 @@
       <x:c r="C6" s="291"/>
       <x:c r="D6" s="291"/>
       <x:c r="E6" s="291"/>
+      <x:c r="F6" s="291"/>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="296" t="str">
@@ -1860,9 +1879,12 @@
         <x:v>Units Sold</x:v>
       </x:c>
       <x:c r="D7" s="296" t="str">
+        <x:v>Unit Price</x:v>
+      </x:c>
+      <x:c r="E7" s="296" t="str">
         <x:v>Sales Revenue</x:v>
       </x:c>
-      <x:c r="E7" s="296" t="str">
+      <x:c r="F7" s="296" t="str">
         <x:v>Gross Profit</x:v>
       </x:c>
     </x:row>
@@ -1873,13 +1895,14 @@
       <x:c r="B8" s="297" t="n">
         <x:v>46087</x:v>
       </x:c>
-      <x:c r="C8" s="297" t="n">
+      <x:c r="C8" s="299" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="297" t="n">
-        <x:v>3040</x:v>
-      </x:c>
-      <x:c r="E8" s="297" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E8" s="298"/>
+      <x:c r="F8" s="297" t="n">
         <x:v>1216</x:v>
       </x:c>
     </x:row>
@@ -1890,13 +1913,14 @@
       <x:c r="B9" s="297" t="n">
         <x:v>46095</x:v>
       </x:c>
-      <x:c r="C9" s="297" t="n">
+      <x:c r="C9" s="300" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="297" t="n">
-        <x:v>1680</x:v>
-      </x:c>
-      <x:c r="E9" s="297" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E9" s="298"/>
+      <x:c r="F9" s="297" t="n">
         <x:v>672</x:v>
       </x:c>
     </x:row>
@@ -1907,13 +1931,14 @@
       <x:c r="B10" s="297" t="n">
         <x:v>46114</x:v>
       </x:c>
-      <x:c r="C10" s="297" t="n">
+      <x:c r="C10" s="301" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D10" s="297" t="n">
-        <x:v>1360</x:v>
-      </x:c>
-      <x:c r="E10" s="297" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E10" s="298"/>
+      <x:c r="F10" s="297" t="n">
         <x:v>544</x:v>
       </x:c>
     </x:row>
@@ -1924,13 +1949,14 @@
       <x:c r="B11" s="297" t="n">
         <x:v>46131</x:v>
       </x:c>
-      <x:c r="C11" s="297" t="n">
+      <x:c r="C11" s="302" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="297" t="n">
-        <x:v>2480</x:v>
-      </x:c>
-      <x:c r="E11" s="297" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E11" s="298"/>
+      <x:c r="F11" s="297" t="n">
         <x:v>868</x:v>
       </x:c>
     </x:row>
@@ -1941,13 +1967,14 @@
       <x:c r="B12" s="297" t="n">
         <x:v>46149</x:v>
       </x:c>
-      <x:c r="C12" s="297" t="n">
+      <x:c r="C12" s="303" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D12" s="297" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="E12" s="297" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E12" s="298"/>
+      <x:c r="F12" s="297" t="n">
         <x:v>810</x:v>
       </x:c>
     </x:row>
@@ -1958,13 +1985,14 @@
       <x:c r="B13" s="297" t="n">
         <x:v>46165</x:v>
       </x:c>
-      <x:c r="C13" s="297" t="n">
+      <x:c r="C13" s="299" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="297" t="n">
-        <x:v>1520</x:v>
-      </x:c>
-      <x:c r="E13" s="297" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E13" s="298"/>
+      <x:c r="F13" s="297" t="n">
         <x:v>532</x:v>
       </x:c>
     </x:row>
@@ -1975,13 +2003,14 @@
       <x:c r="B14" s="297" t="n">
         <x:v>46166</x:v>
       </x:c>
-      <x:c r="C14" s="297" t="n">
+      <x:c r="C14" s="300" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D14" s="297" t="n">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="E14" s="297" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E14" s="298"/>
+      <x:c r="F14" s="297" t="n">
         <x:v>168</x:v>
       </x:c>
     </x:row>
@@ -1992,13 +2021,14 @@
       <x:c r="B15" s="297" t="n">
         <x:v>46167</x:v>
       </x:c>
-      <x:c r="C15" s="297" t="n">
+      <x:c r="C15" s="301" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D15" s="297" t="n">
-        <x:v>720</x:v>
-      </x:c>
-      <x:c r="E15" s="297" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E15" s="298"/>
+      <x:c r="F15" s="297" t="n">
         <x:v>252</x:v>
       </x:c>
     </x:row>
@@ -2009,13 +2039,14 @@
       <x:c r="B16" s="297" t="n">
         <x:v>46168</x:v>
       </x:c>
-      <x:c r="C16" s="297" t="n">
+      <x:c r="C16" s="302" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="D16" s="297" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="E16" s="297" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="298"/>
+      <x:c r="F16" s="297" t="n">
         <x:v>252</x:v>
       </x:c>
     </x:row>
@@ -2026,13 +2057,14 @@
       <x:c r="B17" s="297" t="n">
         <x:v>46169</x:v>
       </x:c>
-      <x:c r="C17" s="297" t="n">
+      <x:c r="C17" s="303" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D17" s="297" t="n">
-        <x:v>1260</x:v>
-      </x:c>
-      <x:c r="E17" s="297" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E17" s="298"/>
+      <x:c r="F17" s="297" t="n">
         <x:v>567</x:v>
       </x:c>
     </x:row>
@@ -2043,13 +2075,14 @@
       <x:c r="B18" s="297" t="n">
         <x:v>46170</x:v>
       </x:c>
-      <x:c r="C18" s="297" t="n">
+      <x:c r="C18" s="299" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D18" s="297" t="n">
-        <x:v>875</x:v>
-      </x:c>
-      <x:c r="E18" s="297" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E18" s="298"/>
+      <x:c r="F18" s="297" t="n">
         <x:v>262.5</x:v>
       </x:c>
     </x:row>
@@ -2060,13 +2093,14 @@
       <x:c r="B19" s="297" t="n">
         <x:v>46171</x:v>
       </x:c>
-      <x:c r="C19" s="297" t="n">
+      <x:c r="C19" s="300" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D19" s="297" t="n">
-        <x:v>990</x:v>
-      </x:c>
-      <x:c r="E19" s="297" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E19" s="298"/>
+      <x:c r="F19" s="297" t="n">
         <x:v>346.5</x:v>
       </x:c>
     </x:row>
@@ -2077,13 +2111,14 @@
       <x:c r="B20" s="297" t="n">
         <x:v>46172</x:v>
       </x:c>
-      <x:c r="C20" s="297" t="n">
+      <x:c r="C20" s="301" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="297" t="n">
-        <x:v>875</x:v>
-      </x:c>
-      <x:c r="E20" s="297" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E20" s="298"/>
+      <x:c r="F20" s="297" t="n">
         <x:v>350</x:v>
       </x:c>
     </x:row>
@@ -2094,13 +2129,14 @@
       <x:c r="B21" s="297" t="n">
         <x:v>46173</x:v>
       </x:c>
-      <x:c r="C21" s="297" t="n">
+      <x:c r="C21" s="302" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D21" s="297" t="n">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c r="E21" s="297" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E21" s="298"/>
+      <x:c r="F21" s="297" t="n">
         <x:v>432</x:v>
       </x:c>
     </x:row>
@@ -2111,13 +2147,14 @@
       <x:c r="B22" s="297" t="n">
         <x:v>46174</x:v>
       </x:c>
-      <x:c r="C22" s="297" t="n">
+      <x:c r="C22" s="303" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D22" s="297" t="n">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="E22" s="297" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E22" s="298"/>
+      <x:c r="F22" s="297" t="n">
         <x:v>172.8</x:v>
       </x:c>
     </x:row>
@@ -2128,13 +2165,14 @@
       <x:c r="B23" s="297" t="n">
         <x:v>46175</x:v>
       </x:c>
-      <x:c r="C23" s="297" t="n">
+      <x:c r="C23" s="299" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D23" s="297" t="n">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="E23" s="297" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E23" s="298"/>
+      <x:c r="F23" s="297" t="n">
         <x:v>225.4</x:v>
       </x:c>
     </x:row>
@@ -2145,13 +2183,14 @@
       <x:c r="B24" s="297" t="n">
         <x:v>46176</x:v>
       </x:c>
-      <x:c r="C24" s="297" t="n">
+      <x:c r="C24" s="300" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D24" s="297" t="n">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="E24" s="297" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E24" s="298"/>
+      <x:c r="F24" s="297" t="n">
         <x:v>224</x:v>
       </x:c>
     </x:row>
@@ -2162,13 +2201,14 @@
       <x:c r="B25" s="297" t="n">
         <x:v>46177</x:v>
       </x:c>
-      <x:c r="C25" s="297" t="n">
+      <x:c r="C25" s="301" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D25" s="297" t="n">
-        <x:v>1300</x:v>
-      </x:c>
-      <x:c r="E25" s="297" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E25" s="298"/>
+      <x:c r="F25" s="297" t="n">
         <x:v>585</x:v>
       </x:c>
     </x:row>
@@ -2179,13 +2219,14 @@
       <x:c r="B26" s="297" t="n">
         <x:v>46178</x:v>
       </x:c>
-      <x:c r="C26" s="297" t="n">
+      <x:c r="C26" s="302" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="297" t="n">
-        <x:v>814</x:v>
-      </x:c>
-      <x:c r="E26" s="297" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E26" s="298"/>
+      <x:c r="F26" s="297" t="n">
         <x:v>244.2</x:v>
       </x:c>
     </x:row>
@@ -2196,13 +2237,14 @@
       <x:c r="B27" s="297" t="n">
         <x:v>46179</x:v>
       </x:c>
-      <x:c r="C27" s="297" t="n">
+      <x:c r="C27" s="303" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D27" s="297" t="n">
-        <x:v>1080</x:v>
-      </x:c>
-      <x:c r="E27" s="297" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E27" s="298"/>
+      <x:c r="F27" s="297" t="n">
         <x:v>378</x:v>
       </x:c>
     </x:row>
@@ -2213,13 +2255,14 @@
       <x:c r="B28" s="297" t="n">
         <x:v>46180</x:v>
       </x:c>
-      <x:c r="C28" s="297" t="n">
+      <x:c r="C28" s="299" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D28" s="297" t="n">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="E28" s="297" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="298"/>
+      <x:c r="F28" s="297" t="n">
         <x:v>184</x:v>
       </x:c>
     </x:row>
@@ -2230,13 +2273,14 @@
       <x:c r="B29" s="297" t="n">
         <x:v>46181</x:v>
       </x:c>
-      <x:c r="C29" s="297" t="n">
+      <x:c r="C29" s="300" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D29" s="297" t="n">
-        <x:v>864</x:v>
-      </x:c>
-      <x:c r="E29" s="297" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E29" s="298"/>
+      <x:c r="F29" s="297" t="n">
         <x:v>388.8</x:v>
       </x:c>
     </x:row>
@@ -2247,13 +2291,14 @@
       <x:c r="B30" s="297" t="n">
         <x:v>46182</x:v>
       </x:c>
-      <x:c r="C30" s="297" t="n">
+      <x:c r="C30" s="301" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D30" s="297" t="n">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="E30" s="297" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E30" s="298"/>
+      <x:c r="F30" s="297" t="n">
         <x:v>178.2</x:v>
       </x:c>
     </x:row>
@@ -2264,13 +2309,14 @@
       <x:c r="B31" s="297" t="n">
         <x:v>46183</x:v>
       </x:c>
-      <x:c r="C31" s="297" t="n">
+      <x:c r="C31" s="302" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="297" t="n">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="E31" s="297" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E31" s="298"/>
+      <x:c r="F31" s="297" t="n">
         <x:v>224</x:v>
       </x:c>
     </x:row>
@@ -2281,13 +2327,14 @@
       <x:c r="B32" s="297" t="n">
         <x:v>46184</x:v>
       </x:c>
-      <x:c r="C32" s="297" t="n">
+      <x:c r="C32" s="303" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D32" s="297" t="n">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="E32" s="297" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E32" s="298"/>
+      <x:c r="F32" s="297" t="n">
         <x:v>168</x:v>
       </x:c>
     </x:row>
@@ -2298,13 +2345,14 @@
       <x:c r="B33" s="297" t="n">
         <x:v>46185</x:v>
       </x:c>
-      <x:c r="C33" s="297" t="n">
+      <x:c r="C33" s="299" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D33" s="297" t="n">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="E33" s="297" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E33" s="298"/>
+      <x:c r="F33" s="297" t="n">
         <x:v>257.4</x:v>
       </x:c>
     </x:row>
@@ -2314,22 +2362,23 @@
       <x:c r="C34" s="291"/>
       <x:c r="D34" s="291"/>
       <x:c r="E34" s="291"/>
-    </x:row>
-    <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="298" t="str">
-        <x:v>Explain your alert: what should the retail manager notice, and why?</x:v>
-      </x:c>
-      <x:c r="B35" s="298"/>
-      <x:c r="C35" s="298"/>
-      <x:c r="D35" s="298"/>
-      <x:c r="E35" s="298"/>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="299" t="str"/>
-      <x:c r="B36" s="299"/>
-      <x:c r="C36" s="299"/>
-      <x:c r="D36" s="299"/>
-      <x:c r="E36" s="299"/>
+      <x:c r="F34" s="291"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="291"/>
+      <x:c r="B35" s="291"/>
+      <x:c r="C35" s="291"/>
+      <x:c r="D35" s="291"/>
+      <x:c r="E35" s="291"/>
+      <x:c r="F35" s="291"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="291"/>
+      <x:c r="B36" s="291"/>
+      <x:c r="C36" s="291"/>
+      <x:c r="D36" s="291"/>
+      <x:c r="E36" s="291"/>
+      <x:c r="F36" s="291"/>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="291" t="str">
@@ -2338,7 +2387,8 @@
       <x:c r="B37" s="291"/>
       <x:c r="C37" s="291"/>
       <x:c r="D37" s="291"/>
-      <x:c r="E37" s="301"/>
+      <x:c r="E37" s="291"/>
+      <x:c r="F37" s="305"/>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="291" t="str">
@@ -2347,15 +2397,14 @@
       <x:c r="B38" s="291"/>
       <x:c r="C38" s="291"/>
       <x:c r="D38" s="291"/>
-      <x:c r="E38" s="301"/>
+      <x:c r="E38" s="291"/>
+      <x:c r="F38" s="305"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A35:E35"/>
-    <x:mergeCell ref="A36:E36"/>
-    <x:mergeCell ref="A37:D37"/>
-    <x:mergeCell ref="A38:D38"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A37:E37"/>
+    <x:mergeCell ref="A38:E38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rf3f1bc7609974853"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R76648c344d7c462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="Rc86fca8b89dc4175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R2fbc0c0332ac4443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="Rc700cf8344d24302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R7fe12204bc094ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rfe41b454e64449d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rc9c21f3a5e2540ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R300aa298776a483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="Rb72fe647a56547d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R660e5b9bdbea4546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R7e6396aa05504cba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1816,6 +1816,7 @@
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1827,6 +1828,7 @@
       <x:c r="D1" s="294"/>
       <x:c r="E1" s="294"/>
       <x:c r="F1" s="294"/>
+      <x:c r="G1" s="294"/>
     </x:row>
     <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="291"/>
@@ -1835,6 +1837,7 @@
       <x:c r="D2" s="291"/>
       <x:c r="E2" s="291"/>
       <x:c r="F2" s="291"/>
+      <x:c r="G2" s="291"/>
     </x:row>
     <x:row r="3" ht="8" customHeight="1">
       <x:c r="A3" s="291"/>
@@ -1843,6 +1846,7 @@
       <x:c r="D3" s="291"/>
       <x:c r="E3" s="291"/>
       <x:c r="F3" s="291"/>
+      <x:c r="G3" s="291"/>
     </x:row>
     <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="291"/>
@@ -1851,6 +1855,7 @@
       <x:c r="D4" s="291"/>
       <x:c r="E4" s="291"/>
       <x:c r="F4" s="291"/>
+      <x:c r="G4" s="291"/>
     </x:row>
     <x:row r="5" ht="8" customHeight="1">
       <x:c r="A5" s="291"/>
@@ -1859,6 +1864,7 @@
       <x:c r="D5" s="291"/>
       <x:c r="E5" s="291"/>
       <x:c r="F5" s="291"/>
+      <x:c r="G5" s="291"/>
     </x:row>
     <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="291"/>
@@ -1867,6 +1873,7 @@
       <x:c r="D6" s="291"/>
       <x:c r="E6" s="291"/>
       <x:c r="F6" s="291"/>
+      <x:c r="G6" s="291"/>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="296" t="str">
@@ -1885,6 +1892,9 @@
         <x:v>Sales Revenue</x:v>
       </x:c>
       <x:c r="F7" s="296" t="str">
+        <x:v>Expense</x:v>
+      </x:c>
+      <x:c r="G7" s="296" t="str">
         <x:v>Gross Profit</x:v>
       </x:c>
     </x:row>
@@ -1903,8 +1913,9 @@
       </x:c>
       <x:c r="E8" s="298"/>
       <x:c r="F8" s="297" t="n">
-        <x:v>1216</x:v>
-      </x:c>
+        <x:v>1824</x:v>
+      </x:c>
+      <x:c r="G8" s="298"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="297" t="str">
@@ -1921,8 +1932,9 @@
       </x:c>
       <x:c r="E9" s="298"/>
       <x:c r="F9" s="297" t="n">
-        <x:v>672</x:v>
-      </x:c>
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="G9" s="298"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="297" t="str">
@@ -1939,8 +1951,9 @@
       </x:c>
       <x:c r="E10" s="298"/>
       <x:c r="F10" s="297" t="n">
-        <x:v>544</x:v>
-      </x:c>
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="G10" s="298"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="297" t="str">
@@ -1957,8 +1970,9 @@
       </x:c>
       <x:c r="E11" s="298"/>
       <x:c r="F11" s="297" t="n">
-        <x:v>868</x:v>
-      </x:c>
+        <x:v>1612</x:v>
+      </x:c>
+      <x:c r="G11" s="298"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="297" t="str">
@@ -1975,8 +1989,9 @@
       </x:c>
       <x:c r="E12" s="298"/>
       <x:c r="F12" s="297" t="n">
-        <x:v>810</x:v>
-      </x:c>
+        <x:v>1215</x:v>
+      </x:c>
+      <x:c r="G12" s="298"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="297" t="str">
@@ -1993,8 +2008,9 @@
       </x:c>
       <x:c r="E13" s="298"/>
       <x:c r="F13" s="297" t="n">
-        <x:v>532</x:v>
-      </x:c>
+        <x:v>988</x:v>
+      </x:c>
+      <x:c r="G13" s="298"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="297" t="str">
@@ -2011,8 +2027,9 @@
       </x:c>
       <x:c r="E14" s="298"/>
       <x:c r="F14" s="297" t="n">
-        <x:v>168</x:v>
-      </x:c>
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="G14" s="298"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="297" t="str">
@@ -2029,8 +2046,9 @@
       </x:c>
       <x:c r="E15" s="298"/>
       <x:c r="F15" s="297" t="n">
-        <x:v>252</x:v>
-      </x:c>
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="G15" s="298"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="297" t="str">
@@ -2047,8 +2065,9 @@
       </x:c>
       <x:c r="E16" s="298"/>
       <x:c r="F16" s="297" t="n">
-        <x:v>252</x:v>
-      </x:c>
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G16" s="298"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="297" t="str">
@@ -2065,8 +2084,9 @@
       </x:c>
       <x:c r="E17" s="298"/>
       <x:c r="F17" s="297" t="n">
-        <x:v>567</x:v>
-      </x:c>
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="G17" s="298"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="297" t="str">
@@ -2083,8 +2103,9 @@
       </x:c>
       <x:c r="E18" s="298"/>
       <x:c r="F18" s="297" t="n">
-        <x:v>262.5</x:v>
-      </x:c>
+        <x:v>612.5</x:v>
+      </x:c>
+      <x:c r="G18" s="298"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="297" t="str">
@@ -2101,8 +2122,9 @@
       </x:c>
       <x:c r="E19" s="298"/>
       <x:c r="F19" s="297" t="n">
-        <x:v>346.5</x:v>
-      </x:c>
+        <x:v>643.5</x:v>
+      </x:c>
+      <x:c r="G19" s="298"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="297" t="str">
@@ -2119,8 +2141,9 @@
       </x:c>
       <x:c r="E20" s="298"/>
       <x:c r="F20" s="297" t="n">
-        <x:v>350</x:v>
-      </x:c>
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="G20" s="298"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="297" t="str">
@@ -2137,8 +2160,9 @@
       </x:c>
       <x:c r="E21" s="298"/>
       <x:c r="F21" s="297" t="n">
-        <x:v>432</x:v>
-      </x:c>
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="G21" s="298"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="297" t="str">
@@ -2155,8 +2179,9 @@
       </x:c>
       <x:c r="E22" s="298"/>
       <x:c r="F22" s="297" t="n">
-        <x:v>172.8</x:v>
-      </x:c>
+        <x:v>403.2</x:v>
+      </x:c>
+      <x:c r="G22" s="298"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="297" t="str">
@@ -2173,8 +2198,9 @@
       </x:c>
       <x:c r="E23" s="298"/>
       <x:c r="F23" s="297" t="n">
-        <x:v>225.4</x:v>
-      </x:c>
+        <x:v>418.6</x:v>
+      </x:c>
+      <x:c r="G23" s="298"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="297" t="str">
@@ -2191,8 +2217,9 @@
       </x:c>
       <x:c r="E24" s="298"/>
       <x:c r="F24" s="297" t="n">
-        <x:v>224</x:v>
-      </x:c>
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G24" s="298"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="297" t="str">
@@ -2209,8 +2236,9 @@
       </x:c>
       <x:c r="E25" s="298"/>
       <x:c r="F25" s="297" t="n">
-        <x:v>585</x:v>
-      </x:c>
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="G25" s="298"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="297" t="str">
@@ -2227,8 +2255,9 @@
       </x:c>
       <x:c r="E26" s="298"/>
       <x:c r="F26" s="297" t="n">
-        <x:v>244.2</x:v>
-      </x:c>
+        <x:v>569.8</x:v>
+      </x:c>
+      <x:c r="G26" s="298"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="297" t="str">
@@ -2245,8 +2274,9 @@
       </x:c>
       <x:c r="E27" s="298"/>
       <x:c r="F27" s="297" t="n">
-        <x:v>378</x:v>
-      </x:c>
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="G27" s="298"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="297" t="str">
@@ -2263,8 +2293,9 @@
       </x:c>
       <x:c r="E28" s="298"/>
       <x:c r="F28" s="297" t="n">
-        <x:v>184</x:v>
-      </x:c>
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G28" s="298"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="297" t="str">
@@ -2281,8 +2312,9 @@
       </x:c>
       <x:c r="E29" s="298"/>
       <x:c r="F29" s="297" t="n">
-        <x:v>388.8</x:v>
-      </x:c>
+        <x:v>475.2</x:v>
+      </x:c>
+      <x:c r="G29" s="298"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="297" t="str">
@@ -2299,8 +2331,9 @@
       </x:c>
       <x:c r="E30" s="298"/>
       <x:c r="F30" s="297" t="n">
-        <x:v>178.2</x:v>
-      </x:c>
+        <x:v>415.8</x:v>
+      </x:c>
+      <x:c r="G30" s="298"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="297" t="str">
@@ -2317,8 +2350,9 @@
       </x:c>
       <x:c r="E31" s="298"/>
       <x:c r="F31" s="297" t="n">
-        <x:v>224</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="G31" s="298"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="297" t="str">
@@ -2335,8 +2369,9 @@
       </x:c>
       <x:c r="E32" s="298"/>
       <x:c r="F32" s="297" t="n">
-        <x:v>168</x:v>
-      </x:c>
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G32" s="298"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="297" t="str">
@@ -2353,8 +2388,9 @@
       </x:c>
       <x:c r="E33" s="298"/>
       <x:c r="F33" s="297" t="n">
-        <x:v>257.4</x:v>
-      </x:c>
+        <x:v>314.6</x:v>
+      </x:c>
+      <x:c r="G33" s="298"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="291"/>
@@ -2363,6 +2399,7 @@
       <x:c r="D34" s="291"/>
       <x:c r="E34" s="291"/>
       <x:c r="F34" s="291"/>
+      <x:c r="G34" s="291"/>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="291"/>
@@ -2371,6 +2408,7 @@
       <x:c r="D35" s="291"/>
       <x:c r="E35" s="291"/>
       <x:c r="F35" s="291"/>
+      <x:c r="G35" s="291"/>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
       <x:c r="A36" s="291"/>
@@ -2379,6 +2417,7 @@
       <x:c r="D36" s="291"/>
       <x:c r="E36" s="291"/>
       <x:c r="F36" s="291"/>
+      <x:c r="G36" s="291"/>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="291" t="str">
@@ -2389,6 +2428,7 @@
       <x:c r="D37" s="291"/>
       <x:c r="E37" s="291"/>
       <x:c r="F37" s="305"/>
+      <x:c r="G37" s="291"/>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="291" t="str">
@@ -2399,10 +2439,11 @@
       <x:c r="D38" s="291"/>
       <x:c r="E38" s="291"/>
       <x:c r="F38" s="305"/>
+      <x:c r="G38" s="291"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A37:E37"/>
     <x:mergeCell ref="A38:E38"/>
   </x:mergeCells>

--- a/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
+++ b/EXCEL/M02/bus123-excel-m02-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rfe41b454e64449d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rc9c21f3a5e2540ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R300aa298776a483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="Rb72fe647a56547d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R660e5b9bdbea4546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R7e6396aa05504cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R53ff514b7619431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Re136984b893e4987"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Export" sheetId="3" r:id="R1dc91a9fbce44633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manager View" sheetId="4" r:id="R0fb1fa15193147dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="5" r:id="R834dbbfa06454204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" r:id="R9e8b8cbae68e4fa6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,7 +28,7 @@
     <x:numFmt numFmtId="206" formatCode="0.0000"/>
     <x:numFmt numFmtId="207" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="27">
+  <x:fonts count="29">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -185,8 +185,16 @@
       <x:color rgb="FF18261D"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="25">
+  <x:fills count="27">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -308,6 +316,16 @@
         <x:fgColor rgb="FFFFF2C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF217346"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="48">
     <x:border/>
@@ -769,7 +787,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="306">
+  <x:cellXfs count="316">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1445,6 +1463,32 @@
     </x:xf>
     <x:xf numFmtId="207" fontId="24" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1684,18 +1728,18 @@
         <x:v>Finish + Submit</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="95" customHeight="1">
+    <x:row r="5" ht="120" customHeight="1">
       <x:c r="A5" s="101" t="str">
         <x:v>Read the pre-reading. Open this workbook only to observe the tabs. Do not edit Raw Export or begin Manager View yet.</x:v>
       </x:c>
       <x:c r="B5" s="101" t="str">
-        <x:v>Complete the two Live You Try It checkpoints when the slides direct you. The supplied Tidal Goods data is different from the graded Anchor &amp; Oak challenge; focus on formatting decisions.</x:v>
+        <x:v>Use Live You Try It for guided practice: format 26 records, calculate revenue and gross profit, create a table, freeze headings, and apply a conditional-formatting rule.</x:v>
       </x:c>
       <x:c r="C5" s="101" t="str">
-        <x:v>When directed, preserve Raw Export, copy its 10 headers and 24 records, paste values at Manager View!A7, rename the headers, and build the table, formats, widths, alignment, and Freeze Panes.</x:v>
+        <x:v>Work independently. Read Class Challenge for the complete requirements. Use Raw Export as the source and complete the event report on Manager View.</x:v>
       </x:c>
       <x:c r="D5" s="101" t="str">
-        <x:v>Finish four summary formulas, one purposeful conditional-formatting rule, and the 30-second audit. Upload the completed original .xlsx.</x:v>
+        <x:v>Check the report, clear active filters, and submit one .xlsx workbook with Raw Export unchanged and Manager View complete. No separate written response or screenshot is required.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1743,7 +1787,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="109" t="str">
-        <x:v>Build auditable summary formulas with worksheet or table references.</x:v>
+        <x:v>Calculate revenue, profit, and summaries in Live You Try It; apply formatting independently in Manager View.</x:v>
       </x:c>
       <x:c r="C12"/>
       <x:c r="D12"/>
@@ -1753,7 +1797,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="109" t="str">
-        <x:v>Apply conditional formatting for a named business purpose.</x:v>
+        <x:v>Translate a specified business threshold into a conditional-formatting rule.</x:v>
       </x:c>
       <x:c r="C13"/>
       <x:c r="D13"/>
@@ -1782,15 +1826,15 @@
         <x:v>Important boundary</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="78" customHeight="1">
+    <x:row r="18" ht="115" customHeight="1">
       <x:c r="A18" s="101" t="str">
         <x:v>30 points total</x:v>
       </x:c>
       <x:c r="B18" s="101" t="str">
-        <x:v>27 points: source integrity, table/filters, Freeze Panes, number formats, formulas, conditional formatting, and minimum widths.</x:v>
+        <x:v>22 points: required sheets, source and working-copy integrity, table, Freeze Panes, number formats, conditional-format presence, and column widths.</x:v>
       </x:c>
       <x:c r="C18" s="101" t="str">
-        <x:v>3 points: visual hierarchy, alignment, and whether color choices have a clear business purpose.</x:v>
+        <x:v>8 points: exact conditional rule and range, currency precision, readability, alignment, and cleared filters.</x:v>
       </x:c>
       <x:c r="D18" s="101" t="str">
         <x:v>Live You Try It is ungraded practice. The completed Manager View is the only graded activity. Never edit Raw Export.</x:v>
@@ -3276,411 +3320,410 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="309" t="str">
         <x:v>Anchor &amp; Oak Events · Manager View</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-      <x:c r="L1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="97" t="str">
-        <x:v>Begin only when your instructor directs you. Copy Raw Export!A1:J25, paste values at A7, replace the snake_case headers with readable labels, then build the working table. The pale-green cells in C3, F3, I3, and L3 are formula results to complete after class.</x:v>
-      </x:c>
-      <x:c r="B2" s="97"/>
-      <x:c r="C2" s="97"/>
-      <x:c r="D2" s="97"/>
-      <x:c r="E2" s="97"/>
-      <x:c r="F2" s="97"/>
-      <x:c r="G2" s="97"/>
-      <x:c r="H2" s="97"/>
-      <x:c r="I2" s="97"/>
-      <x:c r="J2" s="97"/>
-      <x:c r="K2" s="97"/>
-      <x:c r="L2" s="97"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="B3" s="53" t="str">
-        <x:v>Total Revenue</x:v>
-      </x:c>
-      <x:c r="C3" s="289"/>
-      <x:c r="D3"/>
-      <x:c r="E3" s="53" t="str">
-        <x:v>Total Net Profit</x:v>
-      </x:c>
-      <x:c r="F3" s="289"/>
-      <x:c r="G3"/>
-      <x:c r="H3" s="53" t="str">
-        <x:v>Average Revenue / Event</x:v>
-      </x:c>
-      <x:c r="I3" s="289"/>
-      <x:c r="J3"/>
-      <x:c r="K3" s="53" t="str">
-        <x:v>Total Guests</x:v>
-      </x:c>
-      <x:c r="L3" s="289"/>
-    </x:row>
-    <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="282" t="str">
-        <x:v>AFTER CLASS · Build each summary with a worksheet or table reference, then reconcile it to the 24 detail records. A blank or error-free cell is not evidence of a working formula.</x:v>
-      </x:c>
-      <x:c r="B4" s="283"/>
-      <x:c r="C4" s="283"/>
-      <x:c r="D4" s="283"/>
-      <x:c r="E4" s="283"/>
-      <x:c r="F4" s="283"/>
-      <x:c r="G4" s="283"/>
-      <x:c r="H4" s="283"/>
-      <x:c r="I4" s="283"/>
-      <x:c r="J4" s="283"/>
-      <x:c r="K4" s="283"/>
-      <x:c r="L4" s="284"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="177" t="str">
-        <x:v>IN CLASS · Copy Raw Export!A1:J25 → Paste Values at A7 → rename the 10 headers → convert A7:J31 to a table → format, align, size, and freeze at A8.</x:v>
-      </x:c>
-      <x:c r="B5" s="177"/>
-      <x:c r="C5" s="177"/>
-      <x:c r="D5" s="177"/>
-      <x:c r="E5" s="177"/>
-      <x:c r="F5" s="177"/>
-      <x:c r="G5" s="177"/>
-      <x:c r="H5" s="177"/>
-      <x:c r="I5" s="177"/>
-      <x:c r="J5" s="177"/>
-      <x:c r="K5" s="177"/>
-      <x:c r="L5" s="177"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="242"/>
-      <x:c r="B7" s="243"/>
-      <x:c r="C7" s="243"/>
-      <x:c r="D7" s="243"/>
-      <x:c r="E7" s="243"/>
-      <x:c r="F7" s="243"/>
-      <x:c r="G7" s="243"/>
-      <x:c r="H7" s="243"/>
-      <x:c r="I7" s="243"/>
-      <x:c r="J7" s="244"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="245"/>
-      <x:c r="B8" s="246"/>
-      <x:c r="C8" s="246"/>
-      <x:c r="D8" s="246"/>
-      <x:c r="E8" s="246"/>
-      <x:c r="F8" s="246"/>
-      <x:c r="G8" s="246"/>
-      <x:c r="H8" s="246"/>
-      <x:c r="I8" s="246"/>
-      <x:c r="J8" s="247"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="245"/>
-      <x:c r="B9" s="246"/>
-      <x:c r="C9" s="246"/>
-      <x:c r="D9" s="246"/>
-      <x:c r="E9" s="246"/>
-      <x:c r="F9" s="246"/>
-      <x:c r="G9" s="246"/>
-      <x:c r="H9" s="246"/>
-      <x:c r="I9" s="246"/>
-      <x:c r="J9" s="247"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="245"/>
-      <x:c r="B10" s="246"/>
-      <x:c r="C10" s="246"/>
-      <x:c r="D10" s="246"/>
-      <x:c r="E10" s="246"/>
-      <x:c r="F10" s="246"/>
-      <x:c r="G10" s="246"/>
-      <x:c r="H10" s="246"/>
-      <x:c r="I10" s="246"/>
-      <x:c r="J10" s="247"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="245"/>
-      <x:c r="B11" s="246"/>
-      <x:c r="C11" s="246"/>
-      <x:c r="D11" s="246"/>
-      <x:c r="E11" s="246"/>
-      <x:c r="F11" s="246"/>
-      <x:c r="G11" s="246"/>
-      <x:c r="H11" s="246"/>
-      <x:c r="I11" s="246"/>
-      <x:c r="J11" s="247"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="245"/>
-      <x:c r="B12" s="246"/>
-      <x:c r="C12" s="246"/>
-      <x:c r="D12" s="246"/>
-      <x:c r="E12" s="246"/>
-      <x:c r="F12" s="246"/>
-      <x:c r="G12" s="246"/>
-      <x:c r="H12" s="246"/>
-      <x:c r="I12" s="246"/>
-      <x:c r="J12" s="247"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="245"/>
-      <x:c r="B13" s="246"/>
-      <x:c r="C13" s="246"/>
-      <x:c r="D13" s="246"/>
-      <x:c r="E13" s="246"/>
-      <x:c r="F13" s="246"/>
-      <x:c r="G13" s="246"/>
-      <x:c r="H13" s="246"/>
-      <x:c r="I13" s="246"/>
-      <x:c r="J13" s="247"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="245"/>
-      <x:c r="B14" s="246"/>
-      <x:c r="C14" s="246"/>
-      <x:c r="D14" s="246"/>
-      <x:c r="E14" s="246"/>
-      <x:c r="F14" s="246"/>
-      <x:c r="G14" s="246"/>
-      <x:c r="H14" s="246"/>
-      <x:c r="I14" s="246"/>
-      <x:c r="J14" s="247"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="245"/>
-      <x:c r="B15" s="246"/>
-      <x:c r="C15" s="246"/>
-      <x:c r="D15" s="246"/>
-      <x:c r="E15" s="246"/>
-      <x:c r="F15" s="246"/>
-      <x:c r="G15" s="246"/>
-      <x:c r="H15" s="246"/>
-      <x:c r="I15" s="246"/>
-      <x:c r="J15" s="247"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="245"/>
-      <x:c r="B16" s="246"/>
-      <x:c r="C16" s="246"/>
-      <x:c r="D16" s="246"/>
-      <x:c r="E16" s="246"/>
-      <x:c r="F16" s="246"/>
-      <x:c r="G16" s="246"/>
-      <x:c r="H16" s="246"/>
-      <x:c r="I16" s="246"/>
-      <x:c r="J16" s="247"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="245"/>
-      <x:c r="B17" s="246"/>
-      <x:c r="C17" s="246"/>
-      <x:c r="D17" s="246"/>
-      <x:c r="E17" s="246"/>
-      <x:c r="F17" s="246"/>
-      <x:c r="G17" s="246"/>
-      <x:c r="H17" s="246"/>
-      <x:c r="I17" s="246"/>
-      <x:c r="J17" s="247"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="245"/>
-      <x:c r="B18" s="246"/>
-      <x:c r="C18" s="246"/>
-      <x:c r="D18" s="246"/>
-      <x:c r="E18" s="246"/>
-      <x:c r="F18" s="246"/>
-      <x:c r="G18" s="246"/>
-      <x:c r="H18" s="246"/>
-      <x:c r="I18" s="246"/>
-      <x:c r="J18" s="247"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="245"/>
-      <x:c r="B19" s="246"/>
-      <x:c r="C19" s="246"/>
-      <x:c r="D19" s="246"/>
-      <x:c r="E19" s="246"/>
-      <x:c r="F19" s="246"/>
-      <x:c r="G19" s="246"/>
-      <x:c r="H19" s="246"/>
-      <x:c r="I19" s="246"/>
-      <x:c r="J19" s="247"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="245"/>
-      <x:c r="B20" s="246"/>
-      <x:c r="C20" s="246"/>
-      <x:c r="D20" s="246"/>
-      <x:c r="E20" s="246"/>
-      <x:c r="F20" s="246"/>
-      <x:c r="G20" s="246"/>
-      <x:c r="H20" s="246"/>
-      <x:c r="I20" s="246"/>
-      <x:c r="J20" s="247"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="245"/>
-      <x:c r="B21" s="246"/>
-      <x:c r="C21" s="246"/>
-      <x:c r="D21" s="246"/>
-      <x:c r="E21" s="246"/>
-      <x:c r="F21" s="246"/>
-      <x:c r="G21" s="246"/>
-      <x:c r="H21" s="246"/>
-      <x:c r="I21" s="246"/>
-      <x:c r="J21" s="247"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="245"/>
-      <x:c r="B22" s="246"/>
-      <x:c r="C22" s="246"/>
-      <x:c r="D22" s="246"/>
-      <x:c r="E22" s="246"/>
-      <x:c r="F22" s="246"/>
-      <x:c r="G22" s="246"/>
-      <x:c r="H22" s="246"/>
-      <x:c r="I22" s="246"/>
-      <x:c r="J22" s="247"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="245"/>
-      <x:c r="B23" s="246"/>
-      <x:c r="C23" s="246"/>
-      <x:c r="D23" s="246"/>
-      <x:c r="E23" s="246"/>
-      <x:c r="F23" s="246"/>
-      <x:c r="G23" s="246"/>
-      <x:c r="H23" s="246"/>
-      <x:c r="I23" s="246"/>
-      <x:c r="J23" s="247"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="245"/>
-      <x:c r="B24" s="246"/>
-      <x:c r="C24" s="246"/>
-      <x:c r="D24" s="246"/>
-      <x:c r="E24" s="246"/>
-      <x:c r="F24" s="246"/>
-      <x:c r="G24" s="246"/>
-      <x:c r="H24" s="246"/>
-      <x:c r="I24" s="246"/>
-      <x:c r="J24" s="247"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="245"/>
-      <x:c r="B25" s="246"/>
-      <x:c r="C25" s="246"/>
-      <x:c r="D25" s="246"/>
-      <x:c r="E25" s="246"/>
-      <x:c r="F25" s="246"/>
-      <x:c r="G25" s="246"/>
-      <x:c r="H25" s="246"/>
-      <x:c r="I25" s="246"/>
-      <x:c r="J25" s="247"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="245"/>
-      <x:c r="B26" s="246"/>
-      <x:c r="C26" s="246"/>
-      <x:c r="D26" s="246"/>
-      <x:c r="E26" s="246"/>
-      <x:c r="F26" s="246"/>
-      <x:c r="G26" s="246"/>
-      <x:c r="H26" s="246"/>
-      <x:c r="I26" s="246"/>
-      <x:c r="J26" s="247"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="245"/>
-      <x:c r="B27" s="246"/>
-      <x:c r="C27" s="246"/>
-      <x:c r="D27" s="246"/>
-      <x:c r="E27" s="246"/>
-      <x:c r="F27" s="246"/>
-      <x:c r="G27" s="246"/>
-      <x:c r="H27" s="246"/>
-      <x:c r="I27" s="246"/>
-      <x:c r="J27" s="247"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="245"/>
-      <x:c r="B28" s="246"/>
-      <x:c r="C28" s="246"/>
-      <x:c r="D28" s="246"/>
-      <x:c r="E28" s="246"/>
-      <x:c r="F28" s="246"/>
-      <x:c r="G28" s="246"/>
-      <x:c r="H28" s="246"/>
-      <x:c r="I28" s="246"/>
-      <x:c r="J28" s="247"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="245"/>
-      <x:c r="B29" s="246"/>
-      <x:c r="C29" s="246"/>
-      <x:c r="D29" s="246"/>
-      <x:c r="E29" s="246"/>
-      <x:c r="F29" s="246"/>
-      <x:c r="G29" s="246"/>
-      <x:c r="H29" s="246"/>
-      <x:c r="I29" s="246"/>
-      <x:c r="J29" s="247"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="245"/>
-      <x:c r="B30" s="246"/>
-      <x:c r="C30" s="246"/>
-      <x:c r="D30" s="246"/>
-      <x:c r="E30" s="246"/>
-      <x:c r="F30" s="246"/>
-      <x:c r="G30" s="246"/>
-      <x:c r="H30" s="246"/>
-      <x:c r="I30" s="246"/>
-      <x:c r="J30" s="247"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="248"/>
-      <x:c r="B31" s="249"/>
-      <x:c r="C31" s="249"/>
-      <x:c r="D31" s="249"/>
-      <x:c r="E31" s="249"/>
-      <x:c r="F31" s="249"/>
-      <x:c r="G31" s="249"/>
-      <x:c r="H31" s="249"/>
-      <x:c r="I31" s="249"/>
-      <x:c r="J31" s="250"/>
+      <x:c r="B1" s="309"/>
+      <x:c r="C1" s="309"/>
+      <x:c r="D1" s="309"/>
+      <x:c r="E1" s="309"/>
+      <x:c r="F1" s="309"/>
+      <x:c r="G1" s="309"/>
+      <x:c r="H1" s="309"/>
+      <x:c r="I1" s="309"/>
+      <x:c r="J1" s="309"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="307" t="str">
+        <x:v>Complete the requirements on Class Challenge. Begin your working table at A7.</x:v>
+      </x:c>
+      <x:c r="B2" s="307"/>
+      <x:c r="C2" s="307"/>
+      <x:c r="D2" s="307"/>
+      <x:c r="E2" s="307"/>
+      <x:c r="F2" s="307"/>
+      <x:c r="G2" s="307"/>
+      <x:c r="H2" s="307"/>
+      <x:c r="I2" s="307"/>
+      <x:c r="J2" s="307"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
+    <x:row r="3" ht="8" customHeight="1">
+      <x:c r="A3" s="306"/>
+      <x:c r="B3" s="306"/>
+      <x:c r="C3" s="306"/>
+      <x:c r="D3" s="306"/>
+      <x:c r="E3" s="306"/>
+      <x:c r="F3" s="306"/>
+      <x:c r="G3" s="306"/>
+      <x:c r="H3" s="306"/>
+      <x:c r="I3" s="306"/>
+      <x:c r="J3" s="306"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="8" customHeight="1">
+      <x:c r="A4" s="306"/>
+      <x:c r="B4" s="306"/>
+      <x:c r="C4" s="306"/>
+      <x:c r="D4" s="306"/>
+      <x:c r="E4" s="306"/>
+      <x:c r="F4" s="306"/>
+      <x:c r="G4" s="306"/>
+      <x:c r="H4" s="306"/>
+      <x:c r="I4" s="306"/>
+      <x:c r="J4" s="306"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5" ht="8" customHeight="1">
+      <x:c r="A5" s="306"/>
+      <x:c r="B5" s="306"/>
+      <x:c r="C5" s="306"/>
+      <x:c r="D5" s="306"/>
+      <x:c r="E5" s="306"/>
+      <x:c r="F5" s="306"/>
+      <x:c r="G5" s="306"/>
+      <x:c r="H5" s="306"/>
+      <x:c r="I5" s="306"/>
+      <x:c r="J5" s="306"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+    </x:row>
+    <x:row r="6" ht="8" customHeight="1">
+      <x:c r="A6" s="306"/>
+      <x:c r="B6" s="306"/>
+      <x:c r="C6" s="306"/>
+      <x:c r="D6" s="306"/>
+      <x:c r="E6" s="306"/>
+      <x:c r="F6" s="306"/>
+      <x:c r="G6" s="306"/>
+      <x:c r="H6" s="306"/>
+      <x:c r="I6" s="306"/>
+      <x:c r="J6" s="306"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="306"/>
+      <x:c r="B7" s="306"/>
+      <x:c r="C7" s="306"/>
+      <x:c r="D7" s="306"/>
+      <x:c r="E7" s="306"/>
+      <x:c r="F7" s="306"/>
+      <x:c r="G7" s="306"/>
+      <x:c r="H7" s="306"/>
+      <x:c r="I7" s="306"/>
+      <x:c r="J7" s="306"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="306"/>
+      <x:c r="B8" s="306"/>
+      <x:c r="C8" s="306"/>
+      <x:c r="D8" s="306"/>
+      <x:c r="E8" s="306"/>
+      <x:c r="F8" s="306"/>
+      <x:c r="G8" s="306"/>
+      <x:c r="H8" s="306"/>
+      <x:c r="I8" s="306"/>
+      <x:c r="J8" s="306"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="306"/>
+      <x:c r="B9" s="306"/>
+      <x:c r="C9" s="306"/>
+      <x:c r="D9" s="306"/>
+      <x:c r="E9" s="306"/>
+      <x:c r="F9" s="306"/>
+      <x:c r="G9" s="306"/>
+      <x:c r="H9" s="306"/>
+      <x:c r="I9" s="306"/>
+      <x:c r="J9" s="306"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="306"/>
+      <x:c r="B10" s="306"/>
+      <x:c r="C10" s="306"/>
+      <x:c r="D10" s="306"/>
+      <x:c r="E10" s="306"/>
+      <x:c r="F10" s="306"/>
+      <x:c r="G10" s="306"/>
+      <x:c r="H10" s="306"/>
+      <x:c r="I10" s="306"/>
+      <x:c r="J10" s="306"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="306"/>
+      <x:c r="B11" s="306"/>
+      <x:c r="C11" s="306"/>
+      <x:c r="D11" s="306"/>
+      <x:c r="E11" s="306"/>
+      <x:c r="F11" s="306"/>
+      <x:c r="G11" s="306"/>
+      <x:c r="H11" s="306"/>
+      <x:c r="I11" s="306"/>
+      <x:c r="J11" s="306"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="306"/>
+      <x:c r="B12" s="306"/>
+      <x:c r="C12" s="306"/>
+      <x:c r="D12" s="306"/>
+      <x:c r="E12" s="306"/>
+      <x:c r="F12" s="306"/>
+      <x:c r="G12" s="306"/>
+      <x:c r="H12" s="306"/>
+      <x:c r="I12" s="306"/>
+      <x:c r="J12" s="306"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="306"/>
+      <x:c r="B13" s="306"/>
+      <x:c r="C13" s="306"/>
+      <x:c r="D13" s="306"/>
+      <x:c r="E13" s="306"/>
+      <x:c r="F13" s="306"/>
+      <x:c r="G13" s="306"/>
+      <x:c r="H13" s="306"/>
+      <x:c r="I13" s="306"/>
+      <x:c r="J13" s="306"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="306"/>
+      <x:c r="B14" s="306"/>
+      <x:c r="C14" s="306"/>
+      <x:c r="D14" s="306"/>
+      <x:c r="E14" s="306"/>
+      <x:c r="F14" s="306"/>
+      <x:c r="G14" s="306"/>
+      <x:c r="H14" s="306"/>
+      <x:c r="I14" s="306"/>
+      <x:c r="J14" s="306"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="306"/>
+      <x:c r="B15" s="306"/>
+      <x:c r="C15" s="306"/>
+      <x:c r="D15" s="306"/>
+      <x:c r="E15" s="306"/>
+      <x:c r="F15" s="306"/>
+      <x:c r="G15" s="306"/>
+      <x:c r="H15" s="306"/>
+      <x:c r="I15" s="306"/>
+      <x:c r="J15" s="306"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="306"/>
+      <x:c r="B16" s="306"/>
+      <x:c r="C16" s="306"/>
+      <x:c r="D16" s="306"/>
+      <x:c r="E16" s="306"/>
+      <x:c r="F16" s="306"/>
+      <x:c r="G16" s="306"/>
+      <x:c r="H16" s="306"/>
+      <x:c r="I16" s="306"/>
+      <x:c r="J16" s="306"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="306"/>
+      <x:c r="B17" s="306"/>
+      <x:c r="C17" s="306"/>
+      <x:c r="D17" s="306"/>
+      <x:c r="E17" s="306"/>
+      <x:c r="F17" s="306"/>
+      <x:c r="G17" s="306"/>
+      <x:c r="H17" s="306"/>
+      <x:c r="I17" s="306"/>
+      <x:c r="J17" s="306"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="306"/>
+      <x:c r="B18" s="306"/>
+      <x:c r="C18" s="306"/>
+      <x:c r="D18" s="306"/>
+      <x:c r="E18" s="306"/>
+      <x:c r="F18" s="306"/>
+      <x:c r="G18" s="306"/>
+      <x:c r="H18" s="306"/>
+      <x:c r="I18" s="306"/>
+      <x:c r="J18" s="306"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="306"/>
+      <x:c r="B19" s="306"/>
+      <x:c r="C19" s="306"/>
+      <x:c r="D19" s="306"/>
+      <x:c r="E19" s="306"/>
+      <x:c r="F19" s="306"/>
+      <x:c r="G19" s="306"/>
+      <x:c r="H19" s="306"/>
+      <x:c r="I19" s="306"/>
+      <x:c r="J19" s="306"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="306"/>
+      <x:c r="B20" s="306"/>
+      <x:c r="C20" s="306"/>
+      <x:c r="D20" s="306"/>
+      <x:c r="E20" s="306"/>
+      <x:c r="F20" s="306"/>
+      <x:c r="G20" s="306"/>
+      <x:c r="H20" s="306"/>
+      <x:c r="I20" s="306"/>
+      <x:c r="J20" s="306"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="306"/>
+      <x:c r="B21" s="306"/>
+      <x:c r="C21" s="306"/>
+      <x:c r="D21" s="306"/>
+      <x:c r="E21" s="306"/>
+      <x:c r="F21" s="306"/>
+      <x:c r="G21" s="306"/>
+      <x:c r="H21" s="306"/>
+      <x:c r="I21" s="306"/>
+      <x:c r="J21" s="306"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="306"/>
+      <x:c r="B22" s="306"/>
+      <x:c r="C22" s="306"/>
+      <x:c r="D22" s="306"/>
+      <x:c r="E22" s="306"/>
+      <x:c r="F22" s="306"/>
+      <x:c r="G22" s="306"/>
+      <x:c r="H22" s="306"/>
+      <x:c r="I22" s="306"/>
+      <x:c r="J22" s="306"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="306"/>
+      <x:c r="B23" s="306"/>
+      <x:c r="C23" s="306"/>
+      <x:c r="D23" s="306"/>
+      <x:c r="E23" s="306"/>
+      <x:c r="F23" s="306"/>
+      <x:c r="G23" s="306"/>
+      <x:c r="H23" s="306"/>
+      <x:c r="I23" s="306"/>
+      <x:c r="J23" s="306"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="306"/>
+      <x:c r="B24" s="306"/>
+      <x:c r="C24" s="306"/>
+      <x:c r="D24" s="306"/>
+      <x:c r="E24" s="306"/>
+      <x:c r="F24" s="306"/>
+      <x:c r="G24" s="306"/>
+      <x:c r="H24" s="306"/>
+      <x:c r="I24" s="306"/>
+      <x:c r="J24" s="306"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="306"/>
+      <x:c r="B25" s="306"/>
+      <x:c r="C25" s="306"/>
+      <x:c r="D25" s="306"/>
+      <x:c r="E25" s="306"/>
+      <x:c r="F25" s="306"/>
+      <x:c r="G25" s="306"/>
+      <x:c r="H25" s="306"/>
+      <x:c r="I25" s="306"/>
+      <x:c r="J25" s="306"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="306"/>
+      <x:c r="B26" s="306"/>
+      <x:c r="C26" s="306"/>
+      <x:c r="D26" s="306"/>
+      <x:c r="E26" s="306"/>
+      <x:c r="F26" s="306"/>
+      <x:c r="G26" s="306"/>
+      <x:c r="H26" s="306"/>
+      <x:c r="I26" s="306"/>
+      <x:c r="J26" s="306"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="306"/>
+      <x:c r="B27" s="306"/>
+      <x:c r="C27" s="306"/>
+      <x:c r="D27" s="306"/>
+      <x:c r="E27" s="306"/>
+      <x:c r="F27" s="306"/>
+      <x:c r="G27" s="306"/>
+      <x:c r="H27" s="306"/>
+      <x:c r="I27" s="306"/>
+      <x:c r="J27" s="306"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="306"/>
+      <x:c r="B28" s="306"/>
+      <x:c r="C28" s="306"/>
+      <x:c r="D28" s="306"/>
+      <x:c r="E28" s="306"/>
+      <x:c r="F28" s="306"/>
+      <x:c r="G28" s="306"/>
+      <x:c r="H28" s="306"/>
+      <x:c r="I28" s="306"/>
+      <x:c r="J28" s="306"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="306"/>
+      <x:c r="B29" s="306"/>
+      <x:c r="C29" s="306"/>
+      <x:c r="D29" s="306"/>
+      <x:c r="E29" s="306"/>
+      <x:c r="F29" s="306"/>
+      <x:c r="G29" s="306"/>
+      <x:c r="H29" s="306"/>
+      <x:c r="I29" s="306"/>
+      <x:c r="J29" s="306"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="306"/>
+      <x:c r="B30" s="306"/>
+      <x:c r="C30" s="306"/>
+      <x:c r="D30" s="306"/>
+      <x:c r="E30" s="306"/>
+      <x:c r="F30" s="306"/>
+      <x:c r="G30" s="306"/>
+      <x:c r="H30" s="306"/>
+      <x:c r="I30" s="306"/>
+      <x:c r="J30" s="306"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="306"/>
+      <x:c r="B31" s="306"/>
+      <x:c r="C31" s="306"/>
+      <x:c r="D31" s="306"/>
+      <x:c r="E31" s="306"/>
+      <x:c r="F31" s="306"/>
+      <x:c r="G31" s="306"/>
+      <x:c r="H31" s="306"/>
+      <x:c r="I31" s="306"/>
+      <x:c r="J31" s="306"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:L1"/>
-    <x:mergeCell ref="A2:L2"/>
-    <x:mergeCell ref="A5:L5"/>
-    <x:mergeCell ref="A4:L4"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3690,265 +3733,186 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="39" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="96" t="str">
-        <x:v>Class Challenge · Manager View Handoff</x:v>
-      </x:c>
-      <x:c r="B1" s="96"/>
-      <x:c r="C1" s="96"/>
-      <x:c r="D1" s="96"/>
-      <x:c r="E1" s="96"/>
-    </x:row>
-    <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="97" t="str">
-        <x:v>Begin only when your instructor directs you. The completed Manager View is graded; Live You Try It remains ungraded practice and Raw Export must remain unchanged.</x:v>
-      </x:c>
-      <x:c r="B2" s="97"/>
-      <x:c r="C2" s="97"/>
-      <x:c r="D2" s="97"/>
-      <x:c r="E2" s="97"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="251" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B4" s="251" t="str">
-        <x:v>Requirement</x:v>
-      </x:c>
-      <x:c r="C4" s="251" t="str">
-        <x:v>Where</x:v>
-      </x:c>
-      <x:c r="D4" s="251" t="str">
-        <x:v>When</x:v>
-      </x:c>
-      <x:c r="E4" s="251" t="str">
-        <x:v>Completion evidence</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="68" customHeight="1">
-      <x:c r="A5" s="262" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="314" t="str">
+        <x:v>Class Challenge · Prepare an Event Report</x:v>
+      </x:c>
+      <x:c r="B1" s="314"/>
+      <x:c r="C1" s="314"/>
+      <x:c r="D1" s="314"/>
+      <x:c r="E1" s="314"/>
+    </x:row>
+    <x:row r="2" ht="60" customHeight="1">
+      <x:c r="A2" s="312" t="str">
+        <x:v>Anchor &amp; Oak’s Raw Export contains 24 event records. Work independently to create a readable, usable report on Manager View. Choose the Excel commands needed to meet these requirements.</x:v>
+      </x:c>
+      <x:c r="B2" s="312"/>
+      <x:c r="C2" s="312"/>
+      <x:c r="D2" s="312"/>
+      <x:c r="E2" s="312"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="311"/>
+      <x:c r="B3" s="311"/>
+      <x:c r="C3" s="311"/>
+      <x:c r="D3" s="311"/>
+      <x:c r="E3" s="311"/>
+    </x:row>
+    <x:row r="4" ht="45" customHeight="1">
+      <x:c r="A4" s="315" t="str">
+        <x:v>Readable headings: Event ID, Event, Event Date, Event Type, Guests, Revenue, Catering Cost, Staffing Cost, Net Profit, Status.</x:v>
+      </x:c>
+      <x:c r="B4" s="315"/>
+      <x:c r="C4" s="315"/>
+      <x:c r="D4" s="315"/>
+      <x:c r="E4" s="315"/>
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="311"/>
+      <x:c r="B5" s="311"/>
+      <x:c r="C5" s="311"/>
+      <x:c r="D5" s="311"/>
+      <x:c r="E5" s="311"/>
+    </x:row>
+    <x:row r="6" ht="50" customHeight="1">
+      <x:c r="A6" s="311" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="259" t="str">
-        <x:v>Preserve every Raw Export header and record exactly as provided.</x:v>
-      </x:c>
-      <x:c r="C5" s="259" t="str">
-        <x:v>Raw Export!A1:J25</x:v>
-      </x:c>
-      <x:c r="D5" s="259" t="str">
-        <x:v>Always</x:v>
-      </x:c>
-      <x:c r="E5" s="259" t="str">
-        <x:v>No values, rows, columns, or sheet names changed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="82" customHeight="1">
-      <x:c r="A6" s="262" t="str">
+      <x:c r="B6" s="312" t="str">
+        <x:v>Leave Raw Export unchanged. Copy all headers and records to Manager View beginning at A7, using Paste Values.</x:v>
+      </x:c>
+      <x:c r="C6" s="312"/>
+      <x:c r="D6" s="312"/>
+      <x:c r="E6" s="312"/>
+    </x:row>
+    <x:row r="7" ht="50" customHeight="1">
+      <x:c r="A7" s="311" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="259" t="str">
-        <x:v>Copy Raw Export!A1:J25, use Paste Values beginning at Manager View!A7, then replace the 10 snake_case headers with readable labels without changing any detail value.</x:v>
-      </x:c>
-      <x:c r="C6" s="259" t="str">
-        <x:v>Raw Export → Manager View!A7:J31</x:v>
-      </x:c>
-      <x:c r="D6" s="259" t="str">
-        <x:v>In class · first</x:v>
-      </x:c>
-      <x:c r="E6" s="259" t="str">
-        <x:v>All 24 records and 10 readable headers appear; Raw Export remains unchanged</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="68" customHeight="1">
-      <x:c r="A7" s="262" t="str">
+      <x:c r="B7" s="312" t="str">
+        <x:v>Replace the exported headings with the readable headings listed above. Preserve every detail value, including Net Profit.</x:v>
+      </x:c>
+      <x:c r="C7" s="312"/>
+      <x:c r="D7" s="312"/>
+      <x:c r="E7" s="312"/>
+    </x:row>
+    <x:row r="8" ht="50" customHeight="1">
+      <x:c r="A8" s="311" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="259" t="str">
-        <x:v>Convert the full manager data range into one Excel table and keep filter buttons available.</x:v>
-      </x:c>
-      <x:c r="C7" s="259" t="str">
-        <x:v>Manager View!A7:J31</x:v>
-      </x:c>
-      <x:c r="D7" s="259" t="str">
-        <x:v>In class</x:v>
-      </x:c>
-      <x:c r="E7" s="259" t="str">
-        <x:v>All 24 records and headers are inside one table</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="262" t="str">
+      <x:c r="B8" s="312" t="str">
+        <x:v>Create one Excel table containing all 24 records. Choose a readable style and retain the filter buttons.</x:v>
+      </x:c>
+      <x:c r="C8" s="312"/>
+      <x:c r="D8" s="312"/>
+      <x:c r="E8" s="312"/>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
+      <x:c r="A9" s="311" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="259" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use meaningful formats for the date and business-money columns; format Guests as Number with 0 decimal places.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="259" t="str">
-        <x:v>Manager View</x:v>
-      </x:c>
-      <x:c r="D8" s="259" t="str">
-        <x:v>In class</x:v>
-      </x:c>
-      <x:c r="E8" s="259" t="str">
-        <x:v>Every format communicates what its column means</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="68" customHeight="1">
-      <x:c r="A9" s="262" t="str">
+      <x:c r="B9" s="312" t="str">
+        <x:v>Display Event Date as a recognizable date, Guests as Number with 0 decimal places, and Revenue through Net Profit as currency with two decimal places.</x:v>
+      </x:c>
+      <x:c r="C9" s="312"/>
+      <x:c r="D9" s="312"/>
+      <x:c r="E9" s="312"/>
+    </x:row>
+    <x:row r="10" ht="50" customHeight="1">
+      <x:c r="A10" s="311" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="259" t="str">
-        <x:v>Set readable widths and alignment so long labels and values can be scanned without avoidable clipping.</x:v>
-      </x:c>
-      <x:c r="C9" s="259" t="str">
-        <x:v>Manager View!A:J</x:v>
-      </x:c>
-      <x:c r="D9" s="259" t="str">
-        <x:v>In class</x:v>
-      </x:c>
-      <x:c r="E9" s="259" t="str">
-        <x:v>Event names and headings are readable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="68" customHeight="1">
-      <x:c r="A10" s="262" t="str">
+      <x:c r="B10" s="312" t="str">
+        <x:v>Adjust column widths, wrap headings where needed, and use appropriate alignment. All headings and values must be readable.</x:v>
+      </x:c>
+      <x:c r="C10" s="312"/>
+      <x:c r="D10" s="312"/>
+      <x:c r="E10" s="312"/>
+    </x:row>
+    <x:row r="11" ht="50" customHeight="1">
+      <x:c r="A11" s="311" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="259" t="str">
-        <x:v>Select A8 and freeze the rows above it so the actual table header remains visible.</x:v>
-      </x:c>
-      <x:c r="C10" s="259" t="str">
-        <x:v>Manager View</x:v>
-      </x:c>
-      <x:c r="D10" s="259" t="str">
-        <x:v>In class</x:v>
-      </x:c>
-      <x:c r="E10" s="259" t="str">
-        <x:v>Row 7 remains visible while scrolling</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="68" customHeight="1">
-      <x:c r="A11" s="262" t="str">
+      <x:c r="B11" s="312" t="str">
+        <x:v>Freeze the worksheet so the table headings remain visible when you scroll through the records.</x:v>
+      </x:c>
+      <x:c r="C11" s="312"/>
+      <x:c r="D11" s="312"/>
+      <x:c r="E11" s="312"/>
+    </x:row>
+    <x:row r="12" ht="62" customHeight="1">
+      <x:c r="A12" s="311" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="259" t="str">
-        <x:v>Build the four labeled summaries for Total Revenue, Total Net Profit, Average Revenue per Event, and Total Guests.</x:v>
-      </x:c>
-      <x:c r="C11" s="259" t="str">
-        <x:v>Manager View!C3, F3, I3, L3</x:v>
-      </x:c>
-      <x:c r="D11" s="259" t="str">
-        <x:v>After class</x:v>
-      </x:c>
-      <x:c r="E11" s="259" t="str">
-        <x:v>Each result is a formula using worksheet or table references</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="68" customHeight="1">
-      <x:c r="A12" s="262" t="str">
+      <x:c r="B12" s="312" t="str">
+        <x:v>Use conditional formatting to highlight Net Profit values below $2,000. Apply the rule only to Net Profit detail cells and choose a readable highlight.</x:v>
+      </x:c>
+      <x:c r="C12" s="312"/>
+      <x:c r="D12" s="312"/>
+      <x:c r="E12" s="312"/>
+    </x:row>
+    <x:row r="13" ht="50" customHeight="1">
+      <x:c r="A13" s="311" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B12" s="259" t="str">
-        <x:v>Apply one conditional-formatting rule to Net Profit and be able to state its business purpose.</x:v>
-      </x:c>
-      <x:c r="C12" s="259" t="str">
-        <x:v>Manager View!I8:I31</x:v>
-      </x:c>
-      <x:c r="D12" s="259" t="str">
-        <x:v>After class</x:v>
-      </x:c>
-      <x:c r="E12" s="259" t="str">
-        <x:v>The rule helps identify a high, low, or risky result</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="68" customHeight="1">
-      <x:c r="A13" s="262" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" s="259" t="str">
-        <x:v>Create a clear visual hierarchy with readable summaries, a usable table, and purposeful emphasis.</x:v>
-      </x:c>
-      <x:c r="C13" s="259" t="str">
-        <x:v>Manager View</x:v>
-      </x:c>
-      <x:c r="D13" s="259" t="str">
-        <x:v>Final audit</x:v>
-      </x:c>
-      <x:c r="E13" s="259" t="str">
-        <x:v>A manager can understand the workbook in about 30 seconds</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="68" customHeight="1">
-      <x:c r="A14" s="262" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="259" t="str">
-        <x:v>Save and submit the original .xlsx with all required sheet names intact.</x:v>
-      </x:c>
-      <x:c r="C14" s="259" t="str">
-        <x:v>Whole workbook</x:v>
-      </x:c>
-      <x:c r="D14" s="259" t="str">
-        <x:v>Submit</x:v>
-      </x:c>
-      <x:c r="E14" s="259" t="str">
-        <x:v>Workbook opens normally; do not submit PDF or CSV</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="12" customHeight="1">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-    </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="268" t="str">
-        <x:v>Timing</x:v>
-      </x:c>
-      <x:c r="B16" s="268" t="str">
-        <x:v>In class · about 25 minutes</x:v>
-      </x:c>
-      <x:c r="C16" s="268" t="str">
-        <x:v>After class · about 30–40 minutes</x:v>
-      </x:c>
-      <x:c r="D16" s="268" t="str">
-        <x:v>Grading</x:v>
-      </x:c>
-      <x:c r="E16" s="268" t="str">
-        <x:v>Submission</x:v>
-      </x:c>
+      <x:c r="B13" s="312" t="str">
+        <x:v>Check your report, clear any active filters so all 24 records are visible, and save the completed Excel workbook.</x:v>
+      </x:c>
+      <x:c r="C13" s="312"/>
+      <x:c r="D13" s="312"/>
+      <x:c r="E13" s="312"/>
+    </x:row>
+    <x:row r="14" ht="26" customHeight="1">
+      <x:c r="A14" s="311"/>
+      <x:c r="B14" s="311"/>
+      <x:c r="C14" s="311"/>
+      <x:c r="D14" s="311"/>
+      <x:c r="E14" s="311"/>
+    </x:row>
+    <x:row r="15" ht="60" customHeight="1">
+      <x:c r="A15" s="315" t="str">
+        <x:v>SUBMIT ONE .xlsx WORKBOOK: unchanged Raw Export + completed Manager View. Keep the required sheet names. No PDF, CSV, screenshot, or separate written explanation.</x:v>
+      </x:c>
+      <x:c r="B15" s="315"/>
+      <x:c r="C15" s="315"/>
+      <x:c r="D15" s="315"/>
+      <x:c r="E15" s="315"/>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="311"/>
+      <x:c r="B16" s="311"/>
+      <x:c r="C16" s="311"/>
+      <x:c r="D16" s="311"/>
+      <x:c r="E16" s="311"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
-      <x:c r="A17" s="270" t="str">
-        <x:v>Create the working copy before you format.</x:v>
-      </x:c>
-      <x:c r="B17" s="270" t="str">
-        <x:v>Paste values, rename headers, build the table, then add filters, widths, alignment, number formats, and Freeze Panes</x:v>
-      </x:c>
-      <x:c r="C17" s="270" t="str">
-        <x:v>Four formulas, one purposeful rule, 30-second audit</x:v>
-      </x:c>
-      <x:c r="D17" s="270" t="str">
-        <x:v>27 automatic + 3 visual spot-check = 30 points</x:v>
-      </x:c>
-      <x:c r="E17" s="270" t="str">
-        <x:v>Upload the completed .xlsx; do not submit PDF or CSV</x:v>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A4:E4"/>
+    <x:mergeCell ref="B6:E6"/>
+    <x:mergeCell ref="B7:E7"/>
+    <x:mergeCell ref="B8:E8"/>
+    <x:mergeCell ref="B9:E9"/>
+    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="A15:E15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
